--- a/Result/profitability/3011.xlsx
+++ b/Result/profitability/3011.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.4</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.655</v>
+        <v>-0.67625</v>
       </c>
       <c r="N2" t="n">
-        <v>4.75625</v>
+        <v>4.86625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-0.3</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.61</v>
+        <v>-0.60375</v>
       </c>
       <c r="N3" t="n">
-        <v>4.23625</v>
+        <v>4.8775</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.17</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.47875</v>
+        <v>-0.50625</v>
       </c>
       <c r="N4" t="n">
-        <v>5.956250000000001</v>
+        <v>6.04125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.16</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3825</v>
+        <v>-0.47625</v>
       </c>
       <c r="N5" t="n">
-        <v>6.7725</v>
+        <v>7.3925</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1140,7 +1140,7 @@
         <v>-0.39</v>
       </c>
       <c r="N6" t="n">
-        <v>7.23625</v>
+        <v>7.851249999999999</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,16 +1264,16 @@
         <v>-0.06</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.29375</v>
+        <v>-0.2662499999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>7.82875</v>
+        <v>7.38875</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.16</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1425</v>
+        <v>-0.155</v>
       </c>
       <c r="N8" t="n">
-        <v>8.4175</v>
+        <v>9.008749999999999</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1521,7 +1521,7 @@
         <v>-0.08374999999999998</v>
       </c>
       <c r="N9" t="n">
-        <v>8.188750000000001</v>
+        <v>8.188749999999999</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3011</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>121</v>
+      </c>
+      <c r="D75" t="n">
+        <v>112</v>
+      </c>
+      <c r="E75" t="n">
+        <v>9</v>
+      </c>
+      <c r="F75" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-101</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-83.70%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-8</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-109</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-105</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.70875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>4.8675</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.09999999999999998</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.1369863013698629</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>2.004237288135593</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>9.375</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>2.328638497652582</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
